--- a/public/downloads/pricing-matrix-c6f2a9.xlsx
+++ b/public/downloads/pricing-matrix-c6f2a9.xlsx
@@ -6,13 +6,14 @@
   <sheets>
     <sheet sheetId="1" name="📋 How to Use" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Pricing Matrix" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="💰 Your Price Calculator" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="141">
   <si>
     <t>📋 HOW TO USE: Pricing Matrix</t>
   </si>
@@ -360,17 +361,93 @@
   </si>
   <si>
     <t>Minimum retaining wall</t>
+  </si>
+  <si>
+    <t>💰 YOUR CUSTOM PRICE CALCULATOR</t>
+  </si>
+  <si>
+    <t>Enter YOUR costs — prices auto-calculate for every project type</t>
+  </si>
+  <si>
+    <t>YOUR BUSINESS INPUTS</t>
+  </si>
+  <si>
+    <t>Your Hourly Labor Rate:</t>
+  </si>
+  <si>
+    <t>← What you pay your avg crew member/hr</t>
+  </si>
+  <si>
+    <t>Your Overhead %:</t>
+  </si>
+  <si>
+    <t>← Insurance, truck, tools, office — 10-15%</t>
+  </si>
+  <si>
+    <t>Your Target Profit Margin %:</t>
+  </si>
+  <si>
+    <t>← Desired profit after costs — aim 20-30%</t>
+  </si>
+  <si>
+    <t>Your Concrete Cost ($/CY):</t>
+  </si>
+  <si>
+    <t>← Call batch plant for current price</t>
+  </si>
+  <si>
+    <t>YOUR AUTO-CALCULATED PRICING — PER SQUARE FOOT</t>
+  </si>
+  <si>
+    <t>Material $/SF</t>
+  </si>
+  <si>
+    <t>Labor Hrs/SF</t>
+  </si>
+  <si>
+    <t>Labor $/SF</t>
+  </si>
+  <si>
+    <t>Cost/SF</t>
+  </si>
+  <si>
+    <t>YOUR PRICE/SF</t>
+  </si>
+  <si>
+    <t>Min Job $</t>
+  </si>
+  <si>
+    <t>Patio (basic broom)</t>
+  </si>
+  <si>
+    <t>Sidewalk (4")</t>
+  </si>
+  <si>
+    <t>Steps / Landing</t>
+  </si>
+  <si>
+    <t>⚡ QUICK JOB ESTIMATOR</t>
+  </si>
+  <si>
+    <t>Project Square Footage:</t>
+  </si>
+  <si>
+    <t>Your Price/SF (from above):</t>
+  </si>
+  <si>
+    <t>ESTIMATED BID:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.00x"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -422,8 +499,30 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF64748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -443,6 +542,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF10B981"/>
       </patternFill>
     </fill>
   </fills>
@@ -473,7 +582,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -495,6 +604,18 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1929,4 +2050,500 @@
   </mergeCells>
   <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF10B981"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="18">
+        <v>55</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="20">
+        <v>0.12</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="18">
+        <v>150</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="C12" s="22">
+        <v>0.08</v>
+      </c>
+      <c r="D12" s="14">
+        <f>C12*B$5</f>
+      </c>
+      <c r="E12" s="14">
+        <f>B12+D12</f>
+      </c>
+      <c r="F12" s="23">
+        <f>E12*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="G12" s="14">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="14">
+        <v>3</v>
+      </c>
+      <c r="C13" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="D13" s="14">
+        <f>C13*B$5</f>
+      </c>
+      <c r="E13" s="14">
+        <f>B13+D13</f>
+      </c>
+      <c r="F13" s="23">
+        <f>E13*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="G13" s="14">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="B14" s="14">
+        <v>3</v>
+      </c>
+      <c r="C14" s="22">
+        <v>0.12</v>
+      </c>
+      <c r="D14" s="14">
+        <f>C14*B$5</f>
+      </c>
+      <c r="E14" s="14">
+        <f>B14+D14</f>
+      </c>
+      <c r="F14" s="23">
+        <f>E14*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="G14" s="14">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="14">
+        <v>4.5</v>
+      </c>
+      <c r="C15" s="22">
+        <v>0.18</v>
+      </c>
+      <c r="D15" s="14">
+        <f>C15*B$5</f>
+      </c>
+      <c r="E15" s="14">
+        <f>B15+D15</f>
+      </c>
+      <c r="F15" s="23">
+        <f>E15*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="G15" s="14">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="14">
+        <v>5.5</v>
+      </c>
+      <c r="C16" s="22">
+        <v>0.22</v>
+      </c>
+      <c r="D16" s="14">
+        <f>C16*B$5</f>
+      </c>
+      <c r="E16" s="14">
+        <f>B16+D16</f>
+      </c>
+      <c r="F16" s="23">
+        <f>E16*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="G16" s="14">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="B17" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="C17" s="22">
+        <v>0.08</v>
+      </c>
+      <c r="D17" s="14">
+        <f>C17*B$5</f>
+      </c>
+      <c r="E17" s="14">
+        <f>B17+D17</f>
+      </c>
+      <c r="F17" s="23">
+        <f>E17*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="G17" s="14">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="14">
+        <v>4</v>
+      </c>
+      <c r="C18" s="22">
+        <v>0.15</v>
+      </c>
+      <c r="D18" s="14">
+        <f>C18*B$5</f>
+      </c>
+      <c r="E18" s="14">
+        <f>B18+D18</f>
+      </c>
+      <c r="F18" s="23">
+        <f>E18*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="G18" s="14">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="14">
+        <v>5.5</v>
+      </c>
+      <c r="C19" s="22">
+        <v>0.2</v>
+      </c>
+      <c r="D19" s="14">
+        <f>C19*B$5</f>
+      </c>
+      <c r="E19" s="14">
+        <f>B19+D19</f>
+      </c>
+      <c r="F19" s="23">
+        <f>E19*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="G19" s="14">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="C20" s="22">
+        <v>0.09</v>
+      </c>
+      <c r="D20" s="14">
+        <f>C20*B$5</f>
+      </c>
+      <c r="E20" s="14">
+        <f>B20+D20</f>
+      </c>
+      <c r="F20" s="23">
+        <f>E20*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="G20" s="14">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="14">
+        <v>4</v>
+      </c>
+      <c r="C21" s="22">
+        <v>0.16</v>
+      </c>
+      <c r="D21" s="14">
+        <f>C21*B$5</f>
+      </c>
+      <c r="E21" s="14">
+        <f>B21+D21</f>
+      </c>
+      <c r="F21" s="23">
+        <f>E21*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="G21" s="14">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="14">
+        <v>8</v>
+      </c>
+      <c r="C22" s="22">
+        <v>0.3</v>
+      </c>
+      <c r="D22" s="14">
+        <f>C22*B$5</f>
+      </c>
+      <c r="E22" s="14">
+        <f>B22+D22</f>
+      </c>
+      <c r="F22" s="23">
+        <f>E22*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="G22" s="14">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="B23" s="14">
+        <v>6</v>
+      </c>
+      <c r="C23" s="22">
+        <v>0.25</v>
+      </c>
+      <c r="D23" s="14">
+        <f>C23*B$5</f>
+      </c>
+      <c r="E23" s="14">
+        <f>B23+D23</f>
+      </c>
+      <c r="F23" s="23">
+        <f>E23*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="G23" s="14">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="C24" s="22">
+        <v>0.15</v>
+      </c>
+      <c r="D24" s="14">
+        <f>C24*B$5</f>
+      </c>
+      <c r="E24" s="14">
+        <f>B24+D24</f>
+      </c>
+      <c r="F24" s="23">
+        <f>E24*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="G24" s="14">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="B28" s="24">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="B29" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B30" s="27">
+        <f>B28*B29</f>
+      </c>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A27:G27"/>
+  </mergeCells>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
 </file>
--- a/public/downloads/pricing-matrix-c6f2a9.xlsx
+++ b/public/downloads/pricing-matrix-c6f2a9.xlsx
@@ -6,13 +6,14 @@
   <sheets>
     <sheet sheetId="1" name="📋 How to Use" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Pricing Matrix" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Your Price Calculator" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="130">
   <si>
     <t>📋 HOW TO USE: Pricing Matrix</t>
   </si>
@@ -360,6 +361,48 @@
   </si>
   <si>
     <t>Minimum retaining wall</t>
+  </si>
+  <si>
+    <t>YOUR CUSTOM PRICE CALCULATOR</t>
+  </si>
+  <si>
+    <t>Enter YOUR rates below — prices auto-calculate for every project type</t>
+  </si>
+  <si>
+    <t>YOUR RATES</t>
+  </si>
+  <si>
+    <t>Your Hourly Labor Rate:</t>
+  </si>
+  <si>
+    <t>Overhead %:</t>
+  </si>
+  <si>
+    <t>Target Profit Margin %:</t>
+  </si>
+  <si>
+    <t>Concrete Cost ($/CY):</t>
+  </si>
+  <si>
+    <t>YOUR AUTO-CALCULATED PRICING PER SQUARE FOOT</t>
+  </si>
+  <si>
+    <t>Material $/SF</t>
+  </si>
+  <si>
+    <t>Labor Hrs/SF</t>
+  </si>
+  <si>
+    <t>Labor $/SF</t>
+  </si>
+  <si>
+    <t>YOUR Price/SF</t>
+  </si>
+  <si>
+    <t>Min Job Charge</t>
+  </si>
+  <si>
+    <t>Steps/Landing</t>
   </si>
 </sst>
 </file>
@@ -370,7 +413,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -422,8 +465,16 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FF1E293B"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -443,6 +494,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -473,7 +529,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -495,6 +551,11 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1929,4 +1990,379 @@
   </mergeCells>
   <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="15">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6" s="19">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="19">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="B8" s="15">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="C12" s="20">
+        <v>0.08</v>
+      </c>
+      <c r="D12" s="14">
+        <f>C12*B$5</f>
+      </c>
+      <c r="E12" s="21">
+        <f>(B12+D12)*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="F12" s="14">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="14">
+        <v>3</v>
+      </c>
+      <c r="C13" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="D13" s="14">
+        <f>C13*B$5</f>
+      </c>
+      <c r="E13" s="21">
+        <f>(B13+D13)*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="F13" s="14">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="14">
+        <v>3</v>
+      </c>
+      <c r="C14" s="20">
+        <v>0.12</v>
+      </c>
+      <c r="D14" s="14">
+        <f>C14*B$5</f>
+      </c>
+      <c r="E14" s="21">
+        <f>(B14+D14)*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="F14" s="14">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="14">
+        <v>4.5</v>
+      </c>
+      <c r="C15" s="20">
+        <v>0.18</v>
+      </c>
+      <c r="D15" s="14">
+        <f>C15*B$5</f>
+      </c>
+      <c r="E15" s="21">
+        <f>(B15+D15)*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="F15" s="14">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="14">
+        <v>5</v>
+      </c>
+      <c r="C16" s="20">
+        <v>0.22</v>
+      </c>
+      <c r="D16" s="14">
+        <f>C16*B$5</f>
+      </c>
+      <c r="E16" s="21">
+        <f>(B16+D16)*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="F16" s="14">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="C17" s="20">
+        <v>0.08</v>
+      </c>
+      <c r="D17" s="14">
+        <f>C17*B$5</f>
+      </c>
+      <c r="E17" s="21">
+        <f>(B17+D17)*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="F17" s="14">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="14">
+        <v>4</v>
+      </c>
+      <c r="C18" s="20">
+        <v>0.15</v>
+      </c>
+      <c r="D18" s="14">
+        <f>C18*B$5</f>
+      </c>
+      <c r="E18" s="21">
+        <f>(B18+D18)*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="F18" s="14">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="14">
+        <v>5.5</v>
+      </c>
+      <c r="C19" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="D19" s="14">
+        <f>C19*B$5</f>
+      </c>
+      <c r="E19" s="21">
+        <f>(B19+D19)*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="F19" s="14">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="C20" s="20">
+        <v>0.09</v>
+      </c>
+      <c r="D20" s="14">
+        <f>C20*B$5</f>
+      </c>
+      <c r="E20" s="21">
+        <f>(B20+D20)*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="F20" s="14">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="14">
+        <v>4</v>
+      </c>
+      <c r="C21" s="20">
+        <v>0.16</v>
+      </c>
+      <c r="D21" s="14">
+        <f>C21*B$5</f>
+      </c>
+      <c r="E21" s="21">
+        <f>(B21+D21)*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="F21" s="14">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="14">
+        <v>8</v>
+      </c>
+      <c r="C22" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="D22" s="14">
+        <f>C22*B$5</f>
+      </c>
+      <c r="E22" s="21">
+        <f>(B22+D22)*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="F22" s="14">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" s="14">
+        <v>6</v>
+      </c>
+      <c r="C23" s="20">
+        <v>0.25</v>
+      </c>
+      <c r="D23" s="14">
+        <f>C23*B$5</f>
+      </c>
+      <c r="E23" s="21">
+        <f>(B23+D23)*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="F23" s="14">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="C24" s="20">
+        <v>0.15</v>
+      </c>
+      <c r="D24" s="14">
+        <f>C24*B$5</f>
+      </c>
+      <c r="E24" s="21">
+        <f>(B24+D24)*(1+B$6)*(1+B$7)</f>
+      </c>
+      <c r="F24" s="14">
+        <v>1200</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A10:F10"/>
+  </mergeCells>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
 </file>